--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,30 +559,65 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>Additional_Comments</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Threshold_Accept</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Goal_Design_Target</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Lead_Function</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Co_Deliver_Team_Member</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Accept_Goal</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Committed_to_Deliver_by</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -716,22 +751,54 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>Is there a reason to have 3 names for the same reference ?
+HP OJP 9010 All-in-one Printer series
+HP OJP 9010e All-in-One Printer series
+HP OJP 9010 All-in-One Printer
+Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>two names / reference are proposed
+currently 4 references for Office Jet Pro 9010</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Only one name / reference is proposed to customer</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>The Out-Of-Box Experience (OOBE) on 123.hp.com must present only one unique product name/reference for the HP OfficeJet Pro 9010 series to the customer, to minimize user confusion and errors.</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Reduce the number of product reference names for the HP OJP 9010 series to a single, consistent name for customer-facing materials.</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -850,22 +917,49 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Minimum PQ acceptable by region</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Pass intervention rate and NO PQ issue</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>The printer must be able to print on all new and current EM (Evaluation Media) and market segment media, meeting the intervention specification for different media types and climatic conditions for the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Printer must be able to reliably print on all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications for all relevant climatic conditions.</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,22 +1078,49 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer requirement </t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>The printer must function properly and without hardware failure when placed and used on uneven surfaces such as sofas, table cloths, or carpets.</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>The printer must operate reliably without damage when placed and used on uneven surfaces such as sofas, tablecloths, or carpets.</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1127,22 +1248,49 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Assess whether the printer experiences any functional failure when tilted 20 degrees left or right during printing, as per CISS product evaluation protocol.</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Assess whether the printer functions without failure when tilted 20 degrees to the left and right during printing.</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1273,22 +1421,49 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>The printer must maintain print quality and function without issues when printing while placed on a moving trolley.</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>The printer must be able to print on a trolley without print quality (PQ) issues.</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,195 +417,195 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>CMWS
 EMWS</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t xml:space="preserve">Requestor </t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Department (Requestor)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Marconi SF(Non-PDL)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Marconi SF PDL</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Marconi Base</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Marconi PDL Base Specific</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Marconi Hi</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Marconi PDL Hi Specific</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Additional Comments/Information</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Threshold
 (Accept)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Goal
 (Design Target)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Lead Function</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Co Deliver Team Member</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Accept - Goal</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t xml:space="preserve">Committed to Deliver by </t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Additional_Comments</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Department_Requestor</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Additional_Comments_Information</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Threshold_Accept</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Goal_Design_Target</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Lead_Function</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Co_Deliver_Team_Member</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Accept_Goal</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Committed_to_Deliver_by</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -788,7 +776,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Reduce the number of product reference names for the HP OJP 9010 series to a single, consistent name for customer-facing materials.</t>
+          <t>Reduce the number of product name references shown to customers for OfficeJet Pro 9010 series to only one, to minimize user confusion and errors.</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -949,7 +937,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Printer must be able to reliably print on all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications for all relevant climatic conditions.</t>
+          <t>Printer must operate reliably with all new and current EM (Evaluation Media) and market segment media, meeting the minimum print quality (PQ) and intervention specifications for each region and climatic condition as defined for the Manhattan platform.</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1110,7 +1098,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>The printer must operate reliably without damage when placed and used on uneven surfaces such as sofas, tablecloths, or carpets.</t>
+          <t>Printer must function reliably when placed on uneven surfaces (such as sofas, table cloths, or carpets) without failure of the input tray sensor flag or similar components.</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1280,7 +1268,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Assess whether the printer functions without failure when tilted 20 degrees to the left and right during printing.</t>
+          <t>Assess whether the printer maintains full functionality when tilted 20 degrees left and right during printing, with no operational failures.</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1453,7 +1441,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>The printer must be able to print on a trolley without print quality (PQ) issues.</t>
+          <t>Printer must be able to print while placed on a trolley without any print quality issues.</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -776,7 +776,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Reduce the number of product name references shown to customers for OfficeJet Pro 9010 series to only one, to minimize user confusion and errors.</t>
+          <t>Reduce the number of product reference names shown to customers on 123.hp.com for the HP OfficeJet Pro 9010 series to a single, consistent name to minimize user confusion.</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Printer must operate reliably with all new and current EM (Evaluation Media) and market segment media, meeting the minimum print quality (PQ) and intervention specifications for each region and climatic condition as defined for the Manhattan platform.</t>
+          <t>Printer must be able to operate reliably with all new and current EM (Evaluation Media) and market segment media types, meeting regional print quality (PQ) standards and intervention specifications under all Manhattan platform climatic conditions.</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Printer must function reliably when placed on uneven surfaces (such as sofas, table cloths, or carpets) without failure of the input tray sensor flag or similar components.</t>
+          <t>The printer must function without hardware failure, including the input tray sensor flag, when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Assess whether the printer maintains full functionality when tilted 20 degrees left and right during printing, with no operational failures.</t>
+          <t>Assess whether the printer experiences any functional failure when tilted left or right up to 20 degrees during printing.</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Printer must be able to print while placed on a trolley without any print quality issues.</t>
+          <t>Printer must maintain print quality and operate without functional issues when printing while placed on a trolley.</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,70 +542,35 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Department_Requestor</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Additional_Comments_Information</t>
+          <t>Applicable_SKUs</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Threshold_Accept</t>
+          <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Goal_Design_Target</t>
+          <t>Ambiguity_Flag</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Lead_Function</t>
+          <t>Reason_for_Ambiguity</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Co_Deliver_Team_Member</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
-        <is>
-          <t>Accept_Goal</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Committed_to_Deliver_by</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Applicable_SKUs</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Cleaned_Requirement_Text</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Ambiguity_Flag</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Reason_for_Ambiguity</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -739,54 +704,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ?
-HP OJP 9010 All-in-one Printer series
-HP OJP 9010e All-in-One Printer series
-HP OJP 9010 All-in-One Printer
-Have too many names isn't efficient and can induce user errors</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed
-currently 4 references for Office Jet Pro 9010</t>
+          <t>The printer's Out Of Box Experience (OOBE) at 123.hp.com must display only one consistent product name/reference for the HP OfficeJet Pro 9010 series to avoid user confusion.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Only one name / reference is proposed to customer</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Reduce the number of product reference names shown to customers on 123.hp.com for the HP OfficeJet Pro 9010 series to a single, consistent name to minimize user confusion.</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,49 +838,22 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Minimum PQ acceptable by region</t>
+          <t>The printer must reliably print on all current and new EM (Evaluation Media) and media types required by each market segment, meeting regional print quality and intervention specifications for the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Printer must be able to operate reliably with all new and current EM (Evaluation Media) and market segment media types, meeting regional print quality (PQ) standards and intervention specifications under all Manhattan platform climatic conditions.</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1066,49 +972,22 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer requirement </t>
+          <t>The printer must operate as intended when placed on uneven surfaces such as sofas, table cloths, or carpets, without input tray sensor flag breakage or related failures.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>The printer must function without hardware failure, including the input tray sensor flag, when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1236,49 +1115,22 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>Evaluate if the printer experiences any functional failure when tilted 20 degrees left or right during printing, as per CISS product standards.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Assess whether the printer experiences any functional failure when tilted left or right up to 20 degrees during printing.</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1409,49 +1261,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>The printer must maintain print quality and normal operation when printing while placed on a moving trolley.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Printer must maintain print quality and operate without functional issues when printing while placed on a trolley.</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,35 +542,70 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department_Requestor</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
+          <t>Additional_Comments_Information</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Threshold_Accept</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Goal_Design_Target</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Lead_Function</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Co_Deliver_Team_Member</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Accept_Goal</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Committed_to_Deliver_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -704,22 +739,54 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>Is there a reason to have 3 names for the same reference ?
+HP OJP 9010 All-in-one Printer series
+HP OJP 9010e All-in-One Printer series
+HP OJP 9010 All-in-One Printer
+Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>two names / reference are proposed
+currently 4 references for Office Jet Pro 9010</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Only one name / reference is proposed to customer</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>The printer's Out Of Box Experience (OOBE) at 123.hp.com must display only one consistent product name/reference for the HP OfficeJet Pro 9010 series to avoid user confusion.</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Reduce the number of product reference names for HP OJP 9010 series to a maximum of two on 123.hp.com to minimize user confusion.</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -838,22 +905,49 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Minimum PQ acceptable by region</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Pass intervention rate and NO PQ issue</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>The printer must reliably print on all current and new EM (Evaluation Media) and media types required by each market segment, meeting regional print quality and intervention specifications for the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Printer must reliably print on all new and current EM (Evaluation Media) and market segment media, meeting minimum print quality (PQ) standards for each region and passing intervention rate criteria under all relevant climatic conditions for the Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,22 +1066,49 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer requirement </t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>The printer must operate as intended when placed on uneven surfaces such as sofas, table cloths, or carpets, without input tray sensor flag breakage or related failures.</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>The printer must function correctly and without hardware failures (e.g., input tray sensor flag breakage) when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,22 +1236,49 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Evaluate if the printer experiences any functional failure when tilted 20 degrees left or right during printing, as per CISS product standards.</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Assess whether the printer maintains full functionality and print quality when tilted 20 degrees left or right during operation.</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,22 +1409,49 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>The printer must maintain print quality and normal operation when printing while placed on a moving trolley.</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>The printer must print without print quality (PQ) issues when placed on a trolley during operation.</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,195 +429,195 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>CMWS
 EMWS</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Requestor </t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Department (Requestor)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Marconi SF(Non-PDL)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Marconi SF PDL</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Marconi Base</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Marconi PDL Base Specific</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Marconi Hi</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Marconi PDL Hi Specific</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Additional Comments/Information</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Threshold
 (Accept)</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Goal
 (Design Target)</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Lead Function</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Co Deliver Team Member</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Accept - Goal</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Committed to Deliver by </t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Department_Requestor</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Additional_Comments_Information</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Threshold_Accept</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Goal_Design_Target</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Lead_Function</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Co_Deliver_Team_Member</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Accept_Goal</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Committed_to_Deliver_by</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,195 +417,195 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>CMWS
 EMWS</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t xml:space="preserve">Requestor </t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Department (Requestor)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Marconi SF(Non-PDL)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Marconi SF PDL</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Marconi Base</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Marconi PDL Base Specific</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Marconi Hi</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Marconi PDL Hi Specific</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Additional Comments/Information</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Threshold
 (Accept)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Goal
 (Design Target)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Lead Function</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Co Deliver Team Member</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Accept - Goal</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t xml:space="preserve">Committed to Deliver by </t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Department_Requestor</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Additional_Comments_Information</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Additional_Comments</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Threshold_Accept</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Goal_Design_Target</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Lead_Function</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Co_Deliver_Team_Member</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Accept_Goal</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Committed_to_Deliver_by</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -751,17 +739,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ?
-HP OJP 9010 All-in-one Printer series
-HP OJP 9010e All-in-One Printer series
-HP OJP 9010 All-in-One Printer
-Have too many names isn't efficient and can induce user errors</t>
+          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed
-currently 4 references for Office Jet Pro 9010</t>
+          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -788,7 +771,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Reduce the number of product reference names for HP OJP 9010 series to a maximum of two on 123.hp.com to minimize user confusion.</t>
+          <t>Minimize the number of customer-facing product reference names for HP OJP 9010 series to only one name/reference to avoid user confusion.</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -949,7 +932,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Printer must reliably print on all new and current EM (Evaluation Media) and market segment media, meeting minimum print quality (PQ) standards for each region and passing intervention rate criteria under all relevant climatic conditions for the Manhattan platform.</t>
+          <t>The printer must reliably operate with all new and current EM (Evaluation Media) and market segment media types, meeting intervention specifications and minimum print quality (PQ) standards by region under Manhattan platform climatic conditions.</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1110,7 +1093,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>The printer must function correctly and without hardware failures (e.g., input tray sensor flag breakage) when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.</t>
+          <t>The product must operate reliably without mechanical failure (e.g., input tray sensor flag) when placed on uneven surfaces such as sofas, table cloths, or carpets.</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1280,7 +1263,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Assess whether the printer maintains full functionality and print quality when tilted 20 degrees left or right during operation.</t>
+          <t>The product should be evaluated for functional failure when tilted 20 degrees left and right during printing.</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1453,7 +1436,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>The printer must print without print quality (PQ) issues when placed on a trolley during operation.</t>
+          <t>The printer must maintain print quality when operated on a trolley during printing.</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,70 +542,35 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department_Requestor</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Additional_Comments</t>
+          <t>Applicable_SKUs</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Threshold_Accept</t>
+          <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Goal_Design_Target</t>
+          <t>Ambiguity_Flag</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Lead_Function</t>
+          <t>Reason_for_Ambiguity</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Co_Deliver_Team_Member</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
-        <is>
-          <t>Accept_Goal</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Committed_to_Deliver_by</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Applicable_SKUs</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Cleaned_Requirement_Text</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Ambiguity_Flag</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Reason_for_Ambiguity</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -739,49 +704,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
+          <t>Consolidate product naming for HP OfficeJet Pro 9010 series on 123.hp.com to a single reference name to reduce user confusion and errors.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Only one name / reference is proposed to customer</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Minimize the number of customer-facing product reference names for HP OJP 9010 series to only one name/reference to avoid user confusion.</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,49 +838,22 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Minimum PQ acceptable by region</t>
+          <t>Printer must reliably print on all new and current EM (Evaluation Media) and market segment media as specified for the Manhattan platform, meeting minimum print quality by region and intervention rate specifications.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>The printer must reliably operate with all new and current EM (Evaluation Media) and market segment media types, meeting intervention specifications and minimum print quality (PQ) standards by region under Manhattan platform climatic conditions.</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1061,49 +972,22 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer requirement </t>
+          <t>Printer must operate without hardware failure or print quality issues when placed on uneven surfaces such as sofas, tablecloths, or carpets.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>The product must operate reliably without mechanical failure (e.g., input tray sensor flag) when placed on uneven surfaces such as sofas, table cloths, or carpets.</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1231,49 +1115,22 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>Assess functional failure when the printer is tilted 20 degrees left and right during printing.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>The product should be evaluated for functional failure when tilted 20 degrees left and right during printing.</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1404,49 +1261,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>Printer must print without print quality issues when placed on a moving trolley.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>The printer must maintain print quality when operated on a trolley during printing.</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Department_Requestor</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Consolidate product naming for HP OfficeJet Pro 9010 series on 123.hp.com to a single reference name to reduce user confusion and errors.</t>
+          <t>The Out-Of-Box Experience (OOBE) for 123.hp.com must use only one product reference name for the HP OfficeJet Pro 9010 series, to reduce user confusion and errors.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Printer must reliably print on all new and current EM (Evaluation Media) and market segment media as specified for the Manhattan platform, meeting minimum print quality by region and intervention rate specifications.</t>
+          <t>The printer must be capable of reliably operating with all new and current Evaluation Media (EM) and market segment media types, meeting the minimum print quality (PQ) standard for each target region.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Printer must operate without hardware failure or print quality issues when placed on uneven surfaces such as sofas, tablecloths, or carpets.</t>
+          <t>The product must function correctly and without hardware failures when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Assess functional failure when the printer is tilted 20 degrees left and right during printing.</t>
+          <t>The printer should be assessed for functional failures when tilted 20 degrees left or right during printing.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Printer must print without print quality issues when placed on a moving trolley.</t>
+          <t>The printer must be able to print without print quality (PQ) issues when placed on a trolley.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,10 +567,45 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>Additional_Comments</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Threshold_Accept</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Goal_Design_Target</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Lead_Function</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Co_Deliver_Team_Member</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Accept_Goal</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Committed_to_Deliver_by</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -709,7 +744,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>The Out-Of-Box Experience (OOBE) for 123.hp.com must use only one product reference name for the HP OfficeJet Pro 9010 series, to reduce user confusion and errors.</t>
+          <t>Reduce the number of different product names/references shown to customers for the HP OfficeJet Pro 9010 series on 123.hp.com to only one name/reference.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -718,8 +753,35 @@
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Having too many names isn't efficient and can induce user errors.</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Two names/reference are proposed; currently 4 references for Office Jet Pro 9010</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Only one name/reference is proposed to customer</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -843,7 +905,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>The printer must be capable of reliably operating with all new and current Evaluation Media (EM) and market segment media types, meeting the minimum print quality (PQ) standard for each target region.</t>
+          <t>Printer must be able to reliably print on all new and current evaluation media (EM) and market segment media, meeting intervention specifications for different media and climatic conditions for the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -852,8 +914,35 @@
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Minimum PQ acceptable by region</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Pass intervention rate and NO PQ issue</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,7 +1066,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>The product must function correctly and without hardware failures when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.</t>
+          <t>Product must function normally without hardware failures when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -986,8 +1075,35 @@
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>As the complaint on Vasari, input tray sensor flag broken when printer is placed on uneven surface, this issue should be fixed in new product</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Meet customer requirement</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Meet customer requirement</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,7 +1236,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>The printer should be assessed for functional failures when tilted 20 degrees left or right during printing.</t>
+          <t>Assess whether the printer experiences any functional failures if tilted 20 degrees left or right during printing.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1129,8 +1245,35 @@
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Meet customer requirement</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Meet customer requirement</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1266,7 +1409,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>The printer must be able to print without print quality (PQ) issues when placed on a trolley.</t>
+          <t>Printer must maintain print quality and normal operation when placed on a trolley during printing.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1275,8 +1418,35 @@
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Meet customer requirement</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Meet customer requirement</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,19 +542,19 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department_Requestor</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
+          <t>Cleaned_Requirement_Text</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Cleaned_Requirement_Text</t>
-        </is>
-      </c>
       <c r="AB1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
@@ -567,45 +567,10 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Additional_Comments</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
-        <is>
-          <t>Threshold_Accept</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Goal_Design_Target</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Lead_Function</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Co_Deliver_Team_Member</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Accept_Goal</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Committed_to_Deliver_by</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -739,49 +704,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>Reduce the number of product name references for the HP OfficeJet Pro 9010 series on 123.hp.com to a single, consistent name to prevent user confusion.</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Reduce the number of different product names/references shown to customers for the HP OfficeJet Pro 9010 series on 123.hp.com to only one name/reference.</t>
-        </is>
-      </c>
       <c r="AB2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Having too many names isn't efficient and can induce user errors.</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Two names/reference are proposed; currently 4 references for Office Jet Pro 9010</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>Only one name/reference is proposed to customer</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,49 +838,22 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>Ensure the printer operates reliably with all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications across climatic conditions for the Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Printer must be able to reliably print on all new and current evaluation media (EM) and market segment media, meeting intervention specifications for different media and climatic conditions for the Manhattan platform.</t>
-        </is>
-      </c>
       <c r="AB3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Minimum PQ acceptable by region</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1061,49 +972,22 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>The product must function properly and without hardware failure when placed and operated on uneven surfaces such as sofas, tablecloths, or carpets.</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Product must function normally without hardware failures when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.</t>
-        </is>
-      </c>
       <c r="AB4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>As the complaint on Vasari, input tray sensor flag broken when printer is placed on uneven surface, this issue should be fixed in new product</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1231,49 +1115,22 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>Assess whether the printer experiences any functional failure when tilted 20 degrees left or right during printing.</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Assess whether the printer experiences any functional failures if tilted 20 degrees left or right during printing.</t>
-        </is>
-      </c>
       <c r="AB5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1404,49 +1261,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>Verify that the printer maintains print quality and experiences no functional issues when printing while placed on a moving trolley.</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Printer must maintain print quality and normal operation when placed on a trolley during printing.</t>
-        </is>
-      </c>
       <c r="AB6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -542,17 +542,17 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Department_Requestor</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
+          <t>Applicable_SKUs</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
           <t>Cleaned_Requirement_Text</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Applicable_SKUs</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Reduce the number of product name references for the HP OfficeJet Pro 9010 series on 123.hp.com to a single, consistent name to prevent user confusion.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+          <t>Consolidate product naming on 123.hp.com for HP OJP 9010 series to a maximum of two names/references to reduce user confusion and errors.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -838,12 +838,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Ensure the printer operates reliably with all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications across climatic conditions for the Manhattan platform.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+          <t>Printer must reliably operate and meet intervention specifications with all new and current EM (Evaluation Media) and market segment media under various climatic conditions for the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>The product must function properly and without hardware failure when placed and operated on uneven surfaces such as sofas, tablecloths, or carpets.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+          <t>The printer must function correctly and without hardware failure when placed on uneven surfaces such as sofas, table cloths, or carpets.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1115,12 +1115,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>Assess whether the printer experiences any functional failure when tilted 20 degrees left or right during printing.</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Verify that the printer maintains print quality and experiences no functional issues when printing while placed on a moving trolley.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+          <t>The printer must print without print quality issues when placed on a moving trolley.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,7 +542,7 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department_Requestor</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
@@ -567,10 +567,45 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>Additional_Comments_Information</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Threshold_Accept</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Goal_Design_Target</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Lead_Function</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Co_Deliver_Team_Member</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Accept_Goal</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Committed_to_Deliver_by</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -709,7 +744,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Consolidate product naming on 123.hp.com for HP OJP 9010 series to a maximum of two names/references to reduce user confusion and errors.</t>
+          <t>Consolidate product naming for HP OfficeJet Pro 9010 series on 123.hp.com to a single reference name to reduce user confusion and errors.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -718,8 +753,35 @@
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Only one name / reference is proposed to customer</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -843,7 +905,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Printer must reliably operate and meet intervention specifications with all new and current EM (Evaluation Media) and market segment media under various climatic conditions for the Manhattan platform.</t>
+          <t>Printer must reliably operate and meet intervention specifications across all new and current EM (Evaluation Media) and market segment media types and climatic conditions for the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -852,8 +914,35 @@
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Minimum PQ acceptable by region</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Pass intervention rate and NO PQ issue</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,7 +1066,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>The printer must function correctly and without hardware failure when placed on uneven surfaces such as sofas, table cloths, or carpets.</t>
+          <t>Printer must operate without hardware failure, including input tray sensor flag, when placed on uneven surfaces such as sofas, table cloths, or carpets.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -986,8 +1075,35 @@
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer requirement </t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,7 +1236,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Assess whether the printer experiences any functional failure when tilted 20 degrees left or right during printing.</t>
+          <t>Assess printer functionality and failure when tilted 20 degrees left and right during printing operation.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1129,8 +1245,35 @@
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1266,7 +1409,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>The printer must print without print quality issues when placed on a moving trolley.</t>
+          <t>Printer must operate and print without print quality issues when placed on a moving trolley.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1275,8 +1418,35 @@
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,45 +567,40 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Additional_Comments_Information</t>
+          <t>Threshold_Accept</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>Threshold_Accept</t>
+          <t>Goal_Design_Target</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>Goal_Design_Target</t>
+          <t>Lead_Function</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>Lead_Function</t>
+          <t>Co_Deliver_Team_Member</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Co_Deliver_Team_Member</t>
+          <t>Accept_Goal</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>Accept_Goal</t>
+          <t>Committed_to_Deliver_by</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Committed_to_Deliver_by</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -744,7 +739,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Consolidate product naming for HP OfficeJet Pro 9010 series on 123.hp.com to a single reference name to reduce user confusion and errors.</t>
+          <t>Reduce the number of product reference names for HP OfficeJet Pro 9010 series on 123.hp.com to a single, consistent name to minimize user confusion and errors.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -755,33 +750,28 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
+          <t>Two names/reference are proposed. Currently 4 references for Office Jet Pro 9010.</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
+          <t>Only one name/reference is proposed to customer</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>Only one name / reference is proposed to customer</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
           <t>Solution</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr">
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>Drop</t>
         </is>
       </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,7 +895,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Printer must reliably operate and meet intervention specifications across all new and current EM (Evaluation Media) and market segment media types and climatic conditions for the Manhattan platform.</t>
+          <t>Printer must operate reliably and meet intervention specifications when using all new and current EM (Evaluation Media) and market segment media under all relevant climatic conditions for the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -916,33 +906,28 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+          <t>Minimum PQ acceptable by region</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Minimum PQ acceptable by region</t>
+          <t>Pass intervention rate and NO PQ issue</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr">
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>Accept - Threshold</t>
         </is>
       </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1066,7 +1051,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Printer must operate without hardware failure, including input tray sensor flag, when placed on uneven surfaces such as sofas, table cloths, or carpets.</t>
+          <t>The printer must function properly and without damage when placed and used on uneven surfaces such as sofas, tablecloths, or carpets.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1077,33 +1062,28 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+          <t>Meet customer requirement</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer requirement </t>
+          <t>Meet customer requirement</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr">
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>Accept - Threshold</t>
         </is>
       </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1236,7 +1216,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Assess printer functionality and failure when tilted 20 degrees left and right during printing operation.</t>
+          <t>The printer must be assessed for functional failure when tilted 20 degrees left and right during printing.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1247,33 +1227,28 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+          <t>Meet customer requirement</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>Meet customer requirement</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr">
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>Drop</t>
         </is>
       </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1409,7 +1384,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Printer must operate and print without print quality issues when placed on a moving trolley.</t>
+          <t>The printer must print without print quality issues when placed on a trolley.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1420,33 +1395,28 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
+          <t>Meet customer requirement</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>Meet customer requirement</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr">
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>Accept - Threshold</t>
         </is>
       </c>
+      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK6"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,60 +547,65 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
+          <t>Additional_Comments_Information</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Threshold_Accept</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Goal_Design_Target</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Lead_Function</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Co_Deliver_Team_Member</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Accept_Goal</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Committed_to_Deliver_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Threshold_Accept</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Goal_Design_Target</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Lead_Function</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Co_Deliver_Team_Member</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Accept_Goal</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Committed_to_Deliver_by</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -734,44 +739,49 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Only one name / reference is proposed to customer</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Reduce the number of product reference names for HP OfficeJet Pro 9010 series on 123.hp.com to a single, consistent name to minimize user confusion and errors.</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Reduce the number of product reference names shown to customers on 123.hp.com to a single, consistent name for the HP OJP 9010 series, to minimize user confusion and errors.</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Two names/reference are proposed. Currently 4 references for Office Jet Pro 9010.</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Only one name/reference is proposed to customer</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,44 +900,49 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Minimum PQ acceptable by region</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Pass intervention rate and NO PQ issue</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Printer must operate reliably and meet intervention specifications when using all new and current EM (Evaluation Media) and market segment media under all relevant climatic conditions for the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Printer must successfully operate and print on all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications and regional print quality requirements under all relevant climatic conditions for the Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Minimum PQ acceptable by region</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1046,44 +1061,49 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer requirement </t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>The printer must function properly and without damage when placed and used on uneven surfaces such as sofas, tablecloths, or carpets.</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>The printer must operate reliably when placed on uneven surfaces (such as sofas, tablecloths, carpets, etc.), without failure of the input tray sensor flag or similar components.</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1211,44 +1231,49 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>The printer must be assessed for functional failure when tilted 20 degrees left and right during printing.</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>The printer must not experience functional failures when tilted left or right up to 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1379,44 +1404,49 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>The printer must print without print quality issues when placed on a trolley.</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>The printer must maintain print quality and proper function when printing while placed on a moving or stationary trolley.</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,70 +542,35 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Department_Requestor</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Additional_Comments_Information</t>
+          <t>Applicable_SKUs</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Threshold_Accept</t>
+          <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Goal_Design_Target</t>
+          <t>Ambiguity_Flag</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Lead_Function</t>
+          <t>Reason_for_Ambiguity</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Co_Deliver_Team_Member</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
-        <is>
-          <t>Accept_Goal</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Committed_to_Deliver_by</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Applicable_SKUs</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Cleaned_Requirement_Text</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Ambiguity_Flag</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Reason_for_Ambiguity</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -739,49 +704,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
+          <t>Reduce the number of reference names for the HP OfficeJet Pro 9010 series on 123.hp.com to a single, unified name to minimize user confusion and errors.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Only one name / reference is proposed to customer</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Reduce the number of product reference names shown to customers on 123.hp.com to a single, consistent name for the HP OJP 9010 series, to minimize user confusion and errors.</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,49 +838,22 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Minimum PQ acceptable by region</t>
+          <t>Printer must operate reliably and meet intervention specifications across all new and current EM (Evaluation Media) and market segment media under various climatic conditions for the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Printer must successfully operate and print on all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications and regional print quality requirements under all relevant climatic conditions for the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1061,49 +972,22 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer requirement </t>
+          <t>Printer must function properly without mechanical failure (e.g., input tray sensor flag) when placed on uneven surfaces such as sofas, table cloths, or carpets.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>The printer must operate reliably when placed on uneven surfaces (such as sofas, tablecloths, carpets, etc.), without failure of the input tray sensor flag or similar components.</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1231,49 +1115,22 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>Assess whether the printer experiences any functional failure when tilted 20 degrees left or right during printing.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>The printer must not experience functional failures when tilted left or right up to 20 degrees during printing.</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1404,49 +1261,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>Verify that the printer maintains print quality and operates without issues when printing while placed on a moving trolley.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>The printer must maintain print quality and proper function when printing while placed on a moving or stationary trolley.</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,30 +547,50 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
+          <t>Additional_Comments</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Lead_Function</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -704,22 +724,47 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>Is there a reason to have 3 names for the same reference ?
+HP OJP 9010 All-in-one Printer series
+HP OJP 9010e All-in-One Printer series
+HP OJP 9010 All-in-One Printer
+Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>two names / reference are proposed
+currently 4 references for Office Jet Pro 9010</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Only one name / reference is proposed to customer</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Reduce the number of reference names for the HP OfficeJet Pro 9010 series on 123.hp.com to a single, unified name to minimize user confusion and errors.</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>The product naming convention presented to customers on 123.hp.com must be consolidated to a single name/reference per product series (e.g., Office Jet Pro 9010), to reduce confusion and user errors.</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -838,22 +883,42 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Minimum PQ acceptable by region</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Pass intervention rate and NO PQ issue</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Printer must operate reliably and meet intervention specifications across all new and current EM (Evaluation Media) and market segment media under various climatic conditions for the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>The printer must reliably print on all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications for all relevant climatic conditions as defined for the Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,22 +1037,42 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer requirement </t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Printer must function properly without mechanical failure (e.g., input tray sensor flag) when placed on uneven surfaces such as sofas, table cloths, or carpets.</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>The product must function without hardware failure (e.g., input tray sensor flag breakage) when placed and operated on common uneven surfaces such as sofas, table cloths, or carpets.</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,22 +1200,42 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Assess whether the printer experiences any functional failure when tilted 20 degrees left or right during printing.</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>The product must be evaluated for functional failures when tilted left and right up to 20 degrees during printing, as per customer usage scenarios.</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,22 +1366,42 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Verify that the printer maintains print quality and operates without issues when printing while placed on a moving trolley.</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>The printer must maintain print quality and function without issue when printing while placed on a trolley, consistent with standard UBT requirements.</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,30 +567,35 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>Accept_Goal</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -724,17 +729,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ?
-HP OJP 9010 All-in-one Printer series
-HP OJP 9010e All-in-One Printer series
-HP OJP 9010 All-in-One Printer
-Have too many names isn't efficient and can induce user errors</t>
+          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed
-currently 4 references for Office Jet Pro 9010</t>
+          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -749,22 +749,27 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>The product naming convention presented to customers on 123.hp.com must be consolidated to a single name/reference per product series (e.g., Office Jet Pro 9010), to reduce confusion and user errors.</t>
-        </is>
-      </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>The product must present only one unique product name/reference to the customer on 123.hp.com to reduce confusion and user errors.</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,22 +908,27 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>The printer must reliably print on all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications for all relevant climatic conditions as defined for the Manhattan platform.</t>
-        </is>
-      </c>
       <c r="AF3" t="inlineStr">
         <is>
+          <t>The printer must reliably print on all new and current EM (Evaluation Media) and market segment media, meeting minimum print quality (PQ) standards for each region and intervention specifications under all relevant climatic conditions.</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1057,22 +1067,27 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>The product must function without hardware failure (e.g., input tray sensor flag breakage) when placed and operated on common uneven surfaces such as sofas, table cloths, or carpets.</t>
-        </is>
-      </c>
       <c r="AF4" t="inlineStr">
         <is>
+          <t>The product must function properly and without hardware failure (e.g., input tray sensor/flag breakage) when placed and operated on uneven surfaces such as sofas, tablecloths, and carpets.</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1220,22 +1235,27 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>The product must be evaluated for functional failures when tilted left and right up to 20 degrees during printing, as per customer usage scenarios.</t>
-        </is>
-      </c>
       <c r="AF5" t="inlineStr">
         <is>
+          <t>The printer should not experience functional failure if tilted left or right up to 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1386,22 +1406,27 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>The printer must maintain print quality and function without issue when printing while placed on a trolley, consistent with standard UBT requirements.</t>
-        </is>
-      </c>
       <c r="AF6" t="inlineStr">
         <is>
+          <t>The printer must maintain print quality and operate correctly when placed on a moving trolley during printing.</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,22 +542,22 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department_Requestor</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Additional_Comments</t>
+          <t>Additional_Comments_Information</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Threshold</t>
+          <t>Threshold_Accept</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Goal_Design_Target</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
@@ -567,35 +567,45 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>Co_Deliver_Team_Member</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>Accept_Goal</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Committed_to_Deliver_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -729,12 +739,17 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
+          <t>Is there a reason to have 3 names for the same reference ?
+HP OJP 9010 All-in-one Printer series
+HP OJP 9010e All-in-One Printer series
+HP OJP 9010 All-in-One Printer
+Have too many names isn't efficient and can induce user errors</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
+          <t>two names / reference are proposed
+currently 4 references for Office Jet Pro 9010</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -747,29 +762,31 @@
           <t>Solution</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Drop</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>The product must present only one unique product name/reference to the customer on 123.hp.com to reduce confusion and user errors.</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Reduce the number of product reference names shown to customers on 123.hp.com for the OfficeJet Pro 9010 series to a single, consistent name to minimize user confusion.</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,29 +923,31 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Accept - Threshold</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>The printer must reliably print on all new and current EM (Evaluation Media) and market segment media, meeting minimum print quality (PQ) standards for each region and intervention specifications under all relevant climatic conditions.</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>The printer must operate reliably and meet intervention specifications for all new and current EM (Evaluation Media) and market segment media under various climatic conditions defined for the Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1065,29 +1084,31 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>Accept - Threshold</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>The product must function properly and without hardware failure (e.g., input tray sensor/flag breakage) when placed and operated on uneven surfaces such as sofas, tablecloths, and carpets.</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>The printer must function properly when placed on uneven surfaces such as sofas, table cloths, or carpets, without damage to the input tray sensor flag or similar components.</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1233,29 +1254,31 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>Drop</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>The printer should not experience functional failure if tilted left or right up to 20 degrees during printing.</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Assess the printer for functional failures when tilted left and right up to 20 degrees during printing, as per the CISS product evaluation method.</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1404,29 +1427,31 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Accept - Threshold</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>The printer must maintain print quality and operate correctly when placed on a moving trolley during printing.</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>The printer must be able to print on a trolley without causing any print quality (PQ) issues.</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Additional_Comments_Information</t>
+          <t>Additional_Comments</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -739,17 +739,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ?
-HP OJP 9010 All-in-one Printer series
-HP OJP 9010e All-in-One Printer series
-HP OJP 9010 All-in-One Printer
-Have too many names isn't efficient and can induce user errors</t>
+          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed
-currently 4 references for Office Jet Pro 9010</t>
+          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -776,7 +771,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Reduce the number of product reference names shown to customers on 123.hp.com for the OfficeJet Pro 9010 series to a single, consistent name to minimize user confusion.</t>
+          <t>Reduce the number of product reference names for HP OfficeJet Pro 9010 series shown to customers on 123.hp.com to a single, consistent name to prevent user errors.</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -937,7 +932,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>The printer must operate reliably and meet intervention specifications for all new and current EM (Evaluation Media) and market segment media under various climatic conditions defined for the Manhattan platform.</t>
+          <t>Printer must reliably print on all new and current EM (evaluation media) and market segment media, meeting intervention specifications and minimum print quality standards for all targeted regions under relevant climatic conditions.</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1098,7 +1093,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>The printer must function properly when placed on uneven surfaces such as sofas, table cloths, or carpets, without damage to the input tray sensor flag or similar components.</t>
+          <t>The printer must operate reliably without breaking the input tray sensor flag when placed and used on uneven surfaces (e.g., sofa, table cloth, carpet).</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1268,7 +1263,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Assess the printer for functional failures when tilted left and right up to 20 degrees during printing, as per the CISS product evaluation method.</t>
+          <t>Assess whether the printer experiences any functional failures when tilted 20 degrees left or right during printing.</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1441,7 +1436,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>The printer must be able to print on a trolley without causing any print quality (PQ) issues.</t>
+          <t>Printer must be able to print on a trolley without any print quality issues.</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">

--- a/consolidation/outputs/refactored_old_prd.xlsx
+++ b/consolidation/outputs/refactored_old_prd.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,199 +425,164 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>CMWS
 EMWS</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Requestor </t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Department (Requestor)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Marconi SF(Non-PDL)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Marconi SF PDL</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Marconi Base</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Marconi PDL Base Specific</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Marconi Hi</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Marconi PDL Hi Specific</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Additional Comments/Information</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Threshold
 (Accept)</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Goal
 (Design Target)</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Lead Function</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Co Deliver Team Member</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Accept - Goal</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Committed to Deliver by </t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Department_Requestor</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Additional_Comments</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Threshold_Accept</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Goal_Design_Target</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Lead_Function</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Co_Deliver_Team_Member</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Accept_Goal</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Committed_to_Deliver_by</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -739,49 +716,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
+          <t>The out-of-box experience (OOBE) for 123.hp.com must use a single, consistent product name/reference for the HP OfficeJet Pro 9010 series to minimize user confusion and errors.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Only one name / reference is proposed to customer</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Reduce the number of product reference names for HP OfficeJet Pro 9010 series shown to customers on 123.hp.com to a single, consistent name to prevent user errors.</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,49 +850,22 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Minimum PQ acceptable by region</t>
+          <t>The printer must be capable of reliably printing on all new and current EM (Evaluation Media) and market segment media types, meeting intervention and print quality requirements under various climatic conditions for the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Printer must reliably print on all new and current EM (evaluation media) and market segment media, meeting intervention specifications and minimum print quality standards for all targeted regions under relevant climatic conditions.</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1061,49 +984,22 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer requirement </t>
+          <t>The printer must operate normally and without hardware failures (e.g., input tray sensor flag breakage) when placed on uneven surfaces such as sofas, table cloths, or carpets.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>The printer must operate reliably without breaking the input tray sensor flag when placed and used on uneven surfaces (e.g., sofa, table cloth, carpet).</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1231,49 +1127,22 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>Assess whether the printer experiences any functional failure when tilted 20 degrees left or right during printing.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Assess whether the printer experiences any functional failures when tilted 20 degrees left or right during printing.</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1404,49 +1273,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>The printer must maintain print quality and functionality when printing while placed on a moving trolley.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Printer must be able to print on a trolley without any print quality issues.</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
